--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260626.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>34,120,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>34,120,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>28,906,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>28,906,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
